--- a/3th course/МИЭП/lab8.xlsx
+++ b/3th course/МИЭП/lab8.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antonkorolev/Documents/university/3th course/МИЭП/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14225BD5-5FA7-9D40-A096-CA869C12233C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D703F69-7FC1-FF47-9D9D-ADEBDF495C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16880" activeTab="2" xr2:uid="{3381D3DF-D0FD-7A45-9B4C-1AF6F44ED1F4}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="3" xr2:uid="{3381D3DF-D0FD-7A45-9B4C-1AF6F44ED1F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Задача 1 (в4)" sheetId="1" r:id="rId1"/>
     <sheet name="Задача 2 (в4)" sheetId="2" r:id="rId2"/>
     <sheet name="Задача 3 (в4)" sheetId="3" r:id="rId3"/>
+    <sheet name="Задача 4 (в4)" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="solver_adj" localSheetId="0" hidden="1">'Задача 1 (в4)'!$F$2:$F$3</definedName>
@@ -72,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="65">
   <si>
     <t>A1</t>
   </si>
@@ -147,13 +148,279 @@
   </si>
   <si>
     <t>Оптимальные стратегии A3 и B1</t>
+  </si>
+  <si>
+    <t>x1, x2, x3 - доли в продукциях</t>
+  </si>
+  <si>
+    <t>x1, x2, x3 &gt;= 0</t>
+  </si>
+  <si>
+    <t>x1 + x2 + x3 = 1</t>
+  </si>
+  <si>
+    <t>Прямая задача для игрока A</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> X &gt;= 1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">x </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &gt;= 0</t>
+    </r>
+  </si>
+  <si>
+    <t>F(x) = x1 + x2 + x3 -&gt; min</t>
+  </si>
+  <si>
+    <t>2*x1 + 7*x2 + 16*x3 &gt;= 1</t>
+  </si>
+  <si>
+    <t>10*x1 + 6*x2 + 10*x3 &gt;= 1</t>
+  </si>
+  <si>
+    <t>8*x1 + 14*x2 + 7*x3 &gt;= 1</t>
+  </si>
+  <si>
+    <t>Двойственная задача для игрока B</t>
+  </si>
+  <si>
+    <t>AY &lt;= 1</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">y </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &gt;= 0</t>
+    </r>
+  </si>
+  <si>
+    <t>G(Y) = y1 + y2 + y3 -&gt; max</t>
+  </si>
+  <si>
+    <t>2*y1 + 10*y2 + 8*y3 &lt;= 1</t>
+  </si>
+  <si>
+    <t>16*y1 + 10*y2 + 7*y3 &lt;= 1</t>
+  </si>
+  <si>
+    <t>7*y1 + 6*y2 + 14*y3 &lt;= 1</t>
+  </si>
+  <si>
+    <t>y1 = 0 -&gt;</t>
+  </si>
+  <si>
+    <t>6*y2 + 14*y3 = 1</t>
+  </si>
+  <si>
+    <t>10*y2 + 7*y3 = 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">y2 = </t>
+  </si>
+  <si>
+    <t xml:space="preserve">y3 = </t>
+  </si>
+  <si>
+    <t xml:space="preserve">G(Y) = </t>
+  </si>
+  <si>
+    <t>F(x) = G(y) = 1/v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v = </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">x </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = p </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / v -&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">p </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = vx </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>i</t>
+    </r>
+  </si>
+  <si>
+    <t>10 * x1 + 6*x2 + 10*x3 = 1</t>
+  </si>
+  <si>
+    <t>8*x1 + 14*x2 + 7*x3 = 1</t>
+  </si>
+  <si>
+    <t>x1=0</t>
+  </si>
+  <si>
+    <t>p2 = v*x2</t>
+  </si>
+  <si>
+    <t>p3 = v *x3</t>
+  </si>
+  <si>
+    <t>y2 =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">y1 = </t>
+  </si>
+  <si>
+    <t>p1 = v*x1</t>
+  </si>
+  <si>
+    <t>q1 = v*y1</t>
+  </si>
+  <si>
+    <t>q2 = v*y2</t>
+  </si>
+  <si>
+    <t>q3 = v*y3</t>
+  </si>
+  <si>
+    <t>x2 = 4/49</t>
+  </si>
+  <si>
+    <t>x3 = 21/686</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -176,6 +443,20 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow (Основной текст)"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow (Основной текст)"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="5">
@@ -231,7 +512,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -250,6 +531,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1299,4 +1584,332 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00A87396-8CB1-1D49-9001-7761717ACC11}">
+  <dimension ref="A1:P41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>8</v>
+      </c>
+      <c r="E2">
+        <f>MIN(B2:D2)</f>
+        <v>2</v>
+      </c>
+      <c r="F2" s="1">
+        <f>MAX(E2:E4)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>14</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E4" si="0">MIN(B3:D3)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>16</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>7</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <f>MAX(B2:B4)</f>
+        <v>16</v>
+      </c>
+      <c r="C5">
+        <f t="shared" ref="C5:E5" si="1">MAX(C2:C4)</f>
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1">
+        <f>MIN(B5:E5)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D25" t="s">
+        <v>28</v>
+      </c>
+      <c r="H25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="4:16" ht="19" x14ac:dyDescent="0.2">
+      <c r="D26" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="4:16" ht="18" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>30</v>
+      </c>
+      <c r="H27" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D28" t="s">
+        <v>31</v>
+      </c>
+      <c r="H28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="H29" t="s">
+        <v>39</v>
+      </c>
+      <c r="K29" t="s">
+        <v>43</v>
+      </c>
+      <c r="M29" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="N29">
+        <f>4/77</f>
+        <v>5.1948051948051951E-2</v>
+      </c>
+      <c r="O29" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="P29" s="14">
+        <f>SUM(N29:N30)</f>
+        <v>0.11688311688311688</v>
+      </c>
+    </row>
+    <row r="30" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D30" t="s">
+        <v>32</v>
+      </c>
+      <c r="H30" t="s">
+        <v>41</v>
+      </c>
+      <c r="J30" t="s">
+        <v>42</v>
+      </c>
+      <c r="K30" t="s">
+        <v>44</v>
+      </c>
+      <c r="M30" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="N30">
+        <f>5/77</f>
+        <v>6.4935064935064929E-2</v>
+      </c>
+      <c r="O30" s="14"/>
+      <c r="P30" s="14"/>
+    </row>
+    <row r="31" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D31" t="s">
+        <v>33</v>
+      </c>
+      <c r="H31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D32" t="s">
+        <v>34</v>
+      </c>
+      <c r="O32" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="H33" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0</v>
+      </c>
+      <c r="K33" t="s">
+        <v>60</v>
+      </c>
+      <c r="L33">
+        <f>$P$33*I33</f>
+        <v>0</v>
+      </c>
+      <c r="O33" t="s">
+        <v>49</v>
+      </c>
+      <c r="P33" s="1">
+        <f>1/P29</f>
+        <v>8.5555555555555554</v>
+      </c>
+    </row>
+    <row r="34" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="H34" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I34" s="1">
+        <f>N29</f>
+        <v>5.1948051948051951E-2</v>
+      </c>
+      <c r="K34" t="s">
+        <v>61</v>
+      </c>
+      <c r="L34">
+        <f>$P$33*I34</f>
+        <v>0.44444444444444448</v>
+      </c>
+    </row>
+    <row r="35" spans="4:16" ht="18" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" t="s">
+        <v>51</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I35" s="1">
+        <f>N30</f>
+        <v>6.4935064935064929E-2</v>
+      </c>
+      <c r="K35" t="s">
+        <v>62</v>
+      </c>
+      <c r="L35">
+        <f>$P$33*I35</f>
+        <v>0.55555555555555547</v>
+      </c>
+    </row>
+    <row r="36" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D36" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D37" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D39" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E39" t="s">
+        <v>59</v>
+      </c>
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D40" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E40" t="s">
+        <v>55</v>
+      </c>
+      <c r="F40" s="1">
+        <f>(P33*4)/49</f>
+        <v>0.69841269841269837</v>
+      </c>
+    </row>
+    <row r="41" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="D41" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E41" t="s">
+        <v>56</v>
+      </c>
+      <c r="F41" s="1">
+        <f>(P33*21)/686</f>
+        <v>0.26190476190476192</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="O29:O30"/>
+    <mergeCell ref="P29:P30"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/3th course/МИЭП/lab8.xlsx
+++ b/3th course/МИЭП/lab8.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antonkorolev/Documents/university/3th course/МИЭП/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bajsh\Desktop\university\3th course\МИЭП\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D703F69-7FC1-FF47-9D9D-ADEBDF495C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F9B8B5F-E6F9-452E-A139-CE6C1C6A9EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="3" xr2:uid="{3381D3DF-D0FD-7A45-9B4C-1AF6F44ED1F4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{3381D3DF-D0FD-7A45-9B4C-1AF6F44ED1F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Задача 1 (в4)" sheetId="1" r:id="rId1"/>
@@ -20,39 +20,72 @@
   </sheets>
   <definedNames>
     <definedName name="solver_adj" localSheetId="0" hidden="1">'Задача 1 (в4)'!$F$2:$F$3</definedName>
+    <definedName name="solver_adj" localSheetId="3" hidden="1">'Задача 4 (в4)'!$E$31:$E$33</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="3" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">'Задача 1 (в4)'!$F$2:$F$3</definedName>
+    <definedName name="solver_lhs1" localSheetId="3" hidden="1">'Задача 4 (в4)'!$E$31:$E$33</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">'Задача 1 (в4)'!$F$4</definedName>
+    <definedName name="solver_lhs2" localSheetId="3" hidden="1">'Задача 4 (в4)'!$G$31:$G$33</definedName>
     <definedName name="solver_lin" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="3" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="3" hidden="1">0.075</definedName>
     <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="3" hidden="1">2</definedName>
+    <definedName name="solver_nwt" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">'Задача 1 (в4)'!$H$6</definedName>
+    <definedName name="solver_opt" localSheetId="3" hidden="1">'Задача 4 (в4)'!$E$36</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="3" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_rel1" localSheetId="3" hidden="1">3</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rel2" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_rhs1" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rhs2" localSheetId="3" hidden="1">'Задача 4 (в4)'!$H$31:$H$33</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="3" hidden="1">100</definedName>
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="3" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_ver" localSheetId="3" hidden="1">3</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -72,8 +105,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="51">
   <si>
     <t>A1</t>
   </si>
@@ -150,16 +205,16 @@
     <t>Оптимальные стратегии A3 и B1</t>
   </si>
   <si>
-    <t>x1, x2, x3 - доли в продукциях</t>
-  </si>
-  <si>
-    <t>x1, x2, x3 &gt;= 0</t>
-  </si>
-  <si>
-    <t>x1 + x2 + x3 = 1</t>
-  </si>
-  <si>
-    <t>Прямая задача для игрока A</t>
+    <t>p1 = x1 * V</t>
+  </si>
+  <si>
+    <t>p2 = x2 * V</t>
+  </si>
+  <si>
+    <t>p3 = x3 * V</t>
+  </si>
+  <si>
+    <t>v -&gt; max</t>
   </si>
   <si>
     <r>
@@ -170,8 +225,97 @@
         <vertAlign val="superscript"/>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Aptos Narrow (Основной текст)"/>
-        <charset val="204"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">T </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*( xi) &gt;= 1</t>
+    </r>
+  </si>
+  <si>
+    <t>(x1+x2 + x3) -&gt; min</t>
+  </si>
+  <si>
+    <t>q1 = y1 *v</t>
+  </si>
+  <si>
+    <t>q2 = y2 *v</t>
+  </si>
+  <si>
+    <t>q3 = y3 *v</t>
+  </si>
+  <si>
+    <t>v = 1 / (x1+x2+x3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v = (1/y1+y2+y3) </t>
+  </si>
+  <si>
+    <t>v -&gt; min</t>
+  </si>
+  <si>
+    <t>(y1+y2+y3) -&gt; max</t>
+  </si>
+  <si>
+    <t>A  * (yi) &lt;=1</t>
+  </si>
+  <si>
+    <t>Находим вероятности стратегий А</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>T</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">x </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>T</t>
     </r>
@@ -184,20 +328,16 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> X &gt;= 1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">x </t>
+      <t xml:space="preserve">  * (x </t>
     </r>
     <r>
       <rPr>
         <vertAlign val="subscript"/>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Aptos Narrow (Основной текст)"/>
-        <charset val="204"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>i</t>
     </r>
@@ -210,26 +350,23 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> &gt;= 0</t>
+      <t>) &gt;= 1</t>
     </r>
   </si>
   <si>
-    <t>F(x) = x1 + x2 + x3 -&gt; min</t>
-  </si>
-  <si>
-    <t>2*x1 + 7*x2 + 16*x3 &gt;= 1</t>
-  </si>
-  <si>
-    <t>10*x1 + 6*x2 + 10*x3 &gt;= 1</t>
-  </si>
-  <si>
-    <t>8*x1 + 14*x2 + 7*x3 &gt;= 1</t>
-  </si>
-  <si>
-    <t>Двойственная задача для игрока B</t>
-  </si>
-  <si>
-    <t>AY &lt;= 1</t>
+    <t>Σ</t>
+  </si>
+  <si>
+    <t>(x1 + x2 + x3) -&gt; min</t>
+  </si>
+  <si>
+    <t>v=</t>
+  </si>
+  <si>
+    <t>Находим вероятности стратегий B</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
   <si>
     <r>
@@ -240,70 +377,25 @@
         <vertAlign val="subscript"/>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Aptos Narrow (Основной текст)"/>
-        <charset val="204"/>
-      </rPr>
-      <t>j</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
-        <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> &gt;= 0</t>
+      <t>i</t>
     </r>
   </si>
   <si>
-    <t>G(Y) = y1 + y2 + y3 -&gt; max</t>
-  </si>
-  <si>
-    <t>2*y1 + 10*y2 + 8*y3 &lt;= 1</t>
-  </si>
-  <si>
-    <t>16*y1 + 10*y2 + 7*y3 &lt;= 1</t>
-  </si>
-  <si>
-    <t>7*y1 + 6*y2 + 14*y3 &lt;= 1</t>
-  </si>
-  <si>
-    <t>y1 = 0 -&gt;</t>
-  </si>
-  <si>
-    <t>6*y2 + 14*y3 = 1</t>
-  </si>
-  <si>
-    <t>10*y2 + 7*y3 = 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">y2 = </t>
-  </si>
-  <si>
-    <t xml:space="preserve">y3 = </t>
-  </si>
-  <si>
-    <t xml:space="preserve">G(Y) = </t>
-  </si>
-  <si>
-    <t>F(x) = G(y) = 1/v</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v = </t>
-  </si>
-  <si>
     <r>
-      <t xml:space="preserve">x </t>
+      <t xml:space="preserve">A * (y </t>
     </r>
     <r>
       <rPr>
         <vertAlign val="subscript"/>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Aptos Narrow (Основной текст)"/>
-        <charset val="204"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>i</t>
     </r>
@@ -316,111 +408,18 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> = p </t>
+      <t>) &lt;= 1</t>
     </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow (Основной текст)"/>
-        <charset val="204"/>
-      </rPr>
-      <t>i</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> / v -&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">p </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow (Основной текст)"/>
-        <charset val="204"/>
-      </rPr>
-      <t>i</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> = vx </t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow (Основной текст)"/>
-        <charset val="204"/>
-      </rPr>
-      <t>i</t>
-    </r>
-  </si>
-  <si>
-    <t>10 * x1 + 6*x2 + 10*x3 = 1</t>
-  </si>
-  <si>
-    <t>8*x1 + 14*x2 + 7*x3 = 1</t>
-  </si>
-  <si>
-    <t>x1=0</t>
-  </si>
-  <si>
-    <t>p2 = v*x2</t>
-  </si>
-  <si>
-    <t>p3 = v *x3</t>
-  </si>
-  <si>
-    <t>y2 =</t>
-  </si>
-  <si>
-    <t xml:space="preserve">y1 = </t>
-  </si>
-  <si>
-    <t>p1 = v*x1</t>
-  </si>
-  <si>
-    <t>q1 = v*y1</t>
-  </si>
-  <si>
-    <t>q2 = v*y2</t>
-  </si>
-  <si>
-    <t>q3 = v*y3</t>
-  </si>
-  <si>
-    <t>x2 = 4/49</t>
-  </si>
-  <si>
-    <t>x3 = 21/686</t>
+  </si>
+  <si>
+    <t>(y1 + y2 + y3) -&gt; max</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -448,15 +447,32 @@
       <vertAlign val="superscript"/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow (Основной текст)"/>
-      <charset val="204"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <vertAlign val="subscript"/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow (Основной текст)"/>
-      <charset val="204"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -512,7 +528,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -535,6 +551,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -870,12 +899,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A158CF7-E692-1F45-BD2B-FB54BFD8BF6B}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>4</v>
       </c>
@@ -889,7 +918,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -910,7 +939,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -931,7 +960,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -953,7 +982,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -971,7 +1000,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E6">
         <f>SUM(E2:E5)</f>
         <v>0.99999999999999989</v>
@@ -981,7 +1010,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -998,7 +1027,7 @@
         <v>12.999999962146882</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
     </row>
   </sheetData>
@@ -1009,12 +1038,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F30DACAE-3996-154B-9B89-62D52FA45CAF}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" customWidth="1"/>
+    <col min="1" max="1" width="10.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>4</v>
       </c>
@@ -1034,7 +1063,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1059,7 +1088,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1080,7 +1109,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1101,7 +1130,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1122,7 +1151,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1131,7 +1160,7 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <f t="shared" ref="C6:F6" si="1">MAX(C2:C5)</f>
+        <f t="shared" ref="C6:D6" si="1">MAX(C2:C5)</f>
         <v>15</v>
       </c>
       <c r="D6">
@@ -1143,7 +1172,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1152,12 +1181,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1170,9 +1199,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB233ED9-ECB0-A148-880D-C460266E0B9C}">
   <dimension ref="A1:R15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>4</v>
       </c>
@@ -1210,7 +1239,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1257,7 +1286,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1313,7 +1342,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1360,7 +1389,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1407,7 +1436,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
         <v>4</v>
@@ -1441,7 +1470,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
@@ -1487,7 +1516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -1525,11 +1554,11 @@
         <v>5</v>
       </c>
       <c r="N10">
-        <f t="shared" ref="N10:N11" si="0">MIN(L10:M10)</f>
+        <f t="shared" ref="N10" si="0">MIN(L10:M10)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1554,7 +1583,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="K12" s="13" t="s">
         <v>14</v>
       </c>
@@ -1563,7 +1592,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="K14" s="6" t="s">
         <v>23</v>
       </c>
@@ -1572,7 +1601,7 @@
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="K15" s="6" t="s">
         <v>24</v>
       </c>
@@ -1588,10 +1617,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00A87396-8CB1-1D49-9001-7761717ACC11}">
-  <dimension ref="A1:P41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U46"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>4</v>
       </c>
@@ -1608,7 +1637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1630,7 +1659,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1648,7 +1677,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1666,7 +1695,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1675,7 +1704,7 @@
         <v>16</v>
       </c>
       <c r="C5">
-        <f t="shared" ref="C5:E5" si="1">MAX(C2:C4)</f>
+        <f t="shared" ref="C5:D5" si="1">MAX(C2:C4)</f>
         <v>10</v>
       </c>
       <c r="D5">
@@ -1683,7 +1712,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1692,223 +1721,393 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D21" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="17" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D22" t="s">
+      <c r="C11" s="17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="23" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D23" t="s">
+      <c r="D11" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="25" spans="4:16" x14ac:dyDescent="0.2">
+      <c r="F11" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B12" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="F12" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="18" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="19.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="18" x14ac:dyDescent="0.25">
+      <c r="A19" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="E19">
+        <v>3.7890044289698936E-2</v>
+      </c>
+      <c r="G19" cm="1">
+        <f t="array" ref="G19:G21">MMULT(A20:C22,E19:E21)</f>
+        <v>1.0000000024687641</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2</v>
+      </c>
+      <c r="B20">
+        <v>7</v>
+      </c>
+      <c r="C20">
+        <v>16</v>
+      </c>
+      <c r="E20">
+        <v>2.6745913906816979E-2</v>
+      </c>
+      <c r="G20">
+        <v>0.9999999991764208</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>10</v>
+      </c>
+      <c r="B21">
+        <v>6</v>
+      </c>
+      <c r="C21">
+        <v>10</v>
+      </c>
+      <c r="E21">
+        <v>4.6062407283852955E-2</v>
+      </c>
+      <c r="G21">
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>8</v>
+      </c>
+      <c r="B22">
+        <v>14</v>
+      </c>
+      <c r="C22">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24">
+        <f>SUM(E19:E21)</f>
+        <v>0.11069836548036886</v>
+      </c>
+      <c r="F24" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D25" t="s">
-        <v>28</v>
-      </c>
-      <c r="H25" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="4:16" ht="19" x14ac:dyDescent="0.2">
-      <c r="D26" t="s">
-        <v>29</v>
-      </c>
-      <c r="H26" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="4:16" ht="18" x14ac:dyDescent="0.25">
-      <c r="D27" t="s">
-        <v>30</v>
-      </c>
-      <c r="H27" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D28" t="s">
-        <v>31</v>
-      </c>
-      <c r="H28" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="H29" t="s">
-        <v>39</v>
-      </c>
-      <c r="K29" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25">
+        <f>1/E24</f>
+        <v>9.0335570508251006</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D26" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D27" s="21">
+        <f>E19*E25</f>
+        <v>0.34228187674928517</v>
+      </c>
+      <c r="E27" s="21">
+        <f>E20*E25</f>
+        <v>0.24161073915368764</v>
+      </c>
+      <c r="F27" s="21">
+        <f>E21*E25</f>
+        <v>0.41610738409702736</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D28" s="17"/>
+      <c r="E28" s="22">
+        <f>SUM(D27:F27)</f>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="F28" s="17"/>
+    </row>
+    <row r="30" spans="1:8" ht="18.75" x14ac:dyDescent="0.35">
+      <c r="A30" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" t="s">
+        <v>48</v>
+      </c>
+      <c r="G30" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="E31">
+        <v>2.9717681691123158E-3</v>
+      </c>
+      <c r="G31" cm="1">
+        <f t="array" ref="G31:G33">MMULT(A32:C34,E31:E33)</f>
+        <v>1.0000000000000004</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>2</v>
+      </c>
+      <c r="B32">
+        <v>10</v>
+      </c>
+      <c r="C32">
+        <v>8</v>
+      </c>
+      <c r="E32">
+        <v>6.6121842872119502E-2</v>
+      </c>
+      <c r="G32">
+        <v>0.99999999556251917</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>7</v>
+      </c>
+      <c r="B33">
+        <v>6</v>
+      </c>
+      <c r="C33">
+        <v>14</v>
+      </c>
+      <c r="E33">
+        <v>4.1604754367572577E-2</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="R33" s="15"/>
+      <c r="T33" s="14"/>
+      <c r="U33" s="14"/>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>16</v>
+      </c>
+      <c r="B34">
+        <v>10</v>
+      </c>
+      <c r="C34">
+        <v>7</v>
+      </c>
+      <c r="R34" s="15"/>
+      <c r="T34" s="14"/>
+      <c r="U34" s="14"/>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="D36" t="s">
         <v>43</v>
       </c>
-      <c r="M29" s="15" t="s">
+      <c r="E36">
+        <f>SUM(E31:E33)</f>
+        <v>0.1106983654088044</v>
+      </c>
+      <c r="F36" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="15"/>
+      <c r="N36" s="15"/>
+      <c r="U36" s="15"/>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
         <v>45</v>
       </c>
-      <c r="N29">
-        <f>4/77</f>
-        <v>5.1948051948051951E-2</v>
-      </c>
-      <c r="O29" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="P29" s="14">
-        <f>SUM(N29:N30)</f>
-        <v>0.11688311688311688</v>
-      </c>
-    </row>
-    <row r="30" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D30" t="s">
-        <v>32</v>
-      </c>
-      <c r="H30" t="s">
-        <v>41</v>
-      </c>
-      <c r="J30" t="s">
-        <v>42</v>
-      </c>
-      <c r="K30" t="s">
-        <v>44</v>
-      </c>
-      <c r="M30" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="N30">
-        <f>5/77</f>
-        <v>6.4935064935064929E-2</v>
-      </c>
-      <c r="O30" s="14"/>
-      <c r="P30" s="14"/>
-    </row>
-    <row r="31" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D31" t="s">
-        <v>33</v>
-      </c>
-      <c r="H31" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D32" t="s">
-        <v>34</v>
-      </c>
-      <c r="O32" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="33" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="H33" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I33" s="1">
-        <v>0</v>
-      </c>
-      <c r="K33" t="s">
-        <v>60</v>
-      </c>
-      <c r="L33">
-        <f>$P$33*I33</f>
-        <v>0</v>
-      </c>
-      <c r="O33" t="s">
-        <v>49</v>
-      </c>
-      <c r="P33" s="1">
-        <f>1/P29</f>
-        <v>8.5555555555555554</v>
-      </c>
-    </row>
-    <row r="34" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="H34" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I34" s="1">
-        <f>N29</f>
-        <v>5.1948051948051951E-2</v>
-      </c>
-      <c r="K34" t="s">
-        <v>61</v>
-      </c>
-      <c r="L34">
-        <f>$P$33*I34</f>
-        <v>0.44444444444444448</v>
-      </c>
-    </row>
-    <row r="35" spans="4:16" ht="18" x14ac:dyDescent="0.25">
-      <c r="D35" t="s">
-        <v>50</v>
-      </c>
-      <c r="E35" t="s">
-        <v>51</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I35" s="1">
-        <f>N30</f>
-        <v>6.4935064935064929E-2</v>
-      </c>
-      <c r="K35" t="s">
-        <v>62</v>
-      </c>
-      <c r="L35">
-        <f>$P$33*I35</f>
-        <v>0.55555555555555547</v>
-      </c>
-    </row>
-    <row r="36" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D36" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="37" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D37" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="39" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D39" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E39" t="s">
-        <v>59</v>
-      </c>
-      <c r="F39" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D40" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E40" t="s">
-        <v>55</v>
-      </c>
-      <c r="F40" s="1">
-        <f>(P33*4)/49</f>
-        <v>0.69841269841269837</v>
-      </c>
-    </row>
-    <row r="41" spans="4:16" x14ac:dyDescent="0.2">
-      <c r="D41" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E41" t="s">
-        <v>56</v>
-      </c>
-      <c r="F41" s="1">
-        <f>(P33*21)/686</f>
-        <v>0.26190476190476192</v>
-      </c>
+      <c r="E37">
+        <f>1/E36</f>
+        <v>9.0335570566651295</v>
+      </c>
+      <c r="M37" s="15"/>
+      <c r="N37" s="15"/>
+      <c r="U37" s="15"/>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="D38" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="M38" s="15"/>
+      <c r="N38" s="15"/>
+      <c r="U38" s="15"/>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="D39" s="21">
+        <f>E31*E37</f>
+        <v>2.6845637314857371E-2</v>
+      </c>
+      <c r="E39" s="21">
+        <f>E32*E37</f>
+        <v>0.59731544027713801</v>
+      </c>
+      <c r="F39" s="21">
+        <f>E33*E37</f>
+        <v>0.37583892240800465</v>
+      </c>
+      <c r="M39" s="15"/>
+      <c r="N39" s="15"/>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="D40" s="17"/>
+      <c r="E40" s="21">
+        <f>SUM(D39:F39)</f>
+        <v>1</v>
+      </c>
+      <c r="F40" s="17"/>
+      <c r="M40" s="15"/>
+      <c r="N40" s="15"/>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="I42" s="15"/>
+      <c r="K42" s="15"/>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="I43" s="15"/>
+      <c r="K43" s="15"/>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="I44" s="15"/>
+      <c r="K44" s="15"/>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="I45" s="15"/>
+      <c r="K45" s="15"/>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="I46" s="15"/>
+      <c r="K46" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="O29:O30"/>
-    <mergeCell ref="P29:P30"/>
+  <mergeCells count="4">
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="A19:C19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/3th course/МИЭП/lab8.xlsx
+++ b/3th course/МИЭП/lab8.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bajsh\Desktop\university\3th course\МИЭП\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antonkorolev/Documents/university/3th course/МИЭП/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F9B8B5F-E6F9-452E-A139-CE6C1C6A9EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C317BEE0-3A40-1248-AF9B-7149E508A261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{3381D3DF-D0FD-7A45-9B4C-1AF6F44ED1F4}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16880" activeTab="3" xr2:uid="{3381D3DF-D0FD-7A45-9B4C-1AF6F44ED1F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Задача 1 (в4)" sheetId="1" r:id="rId1"/>
@@ -19,73 +19,106 @@
     <sheet name="Задача 4 (в4)" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="solver_adj" localSheetId="0" hidden="1">'Задача 1 (в4)'!$F$2:$F$3</definedName>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">'Задача 1 (в4)'!$E$2:$E$5</definedName>
+    <definedName name="solver_adj" localSheetId="2" hidden="1">'Задача 3 (в4)'!$I$23:$I$24</definedName>
     <definedName name="solver_adj" localSheetId="3" hidden="1">'Задача 4 (в4)'!$E$31:$E$33</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="3" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="3" hidden="1">2147483647</definedName>
-    <definedName name="solver_lhs1" localSheetId="0" hidden="1">'Задача 1 (в4)'!$F$2:$F$3</definedName>
+    <definedName name="solver_lhs1" localSheetId="0" hidden="1">'Задача 1 (в4)'!$E$2:$E$5</definedName>
+    <definedName name="solver_lhs1" localSheetId="2" hidden="1">'Задача 3 (в4)'!$I$23:$I$24</definedName>
     <definedName name="solver_lhs1" localSheetId="3" hidden="1">'Задача 4 (в4)'!$E$31:$E$33</definedName>
-    <definedName name="solver_lhs2" localSheetId="0" hidden="1">'Задача 1 (в4)'!$F$4</definedName>
+    <definedName name="solver_lhs2" localSheetId="0" hidden="1">'Задача 1 (в4)'!$E$6</definedName>
+    <definedName name="solver_lhs2" localSheetId="2" hidden="1">'Задача 3 (в4)'!$K$23:$K$24</definedName>
     <definedName name="solver_lhs2" localSheetId="3" hidden="1">'Задача 4 (в4)'!$G$31:$G$33</definedName>
     <definedName name="solver_lin" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_lin" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_lin" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="3" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="3" hidden="1">0.075</definedName>
     <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_nwt" localSheetId="3" hidden="1">1</definedName>
-    <definedName name="solver_opt" localSheetId="0" hidden="1">'Задача 1 (в4)'!$H$6</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">'Задача 1 (в4)'!$D$7</definedName>
+    <definedName name="solver_opt" localSheetId="2" hidden="1">'Задача 3 (в4)'!$I$27</definedName>
     <definedName name="solver_opt" localSheetId="3" hidden="1">'Задача 4 (в4)'!$E$36</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="3" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_rel1" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_rel1" localSheetId="3" hidden="1">3</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rel2" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_rel2" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_rhs1" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_rhs1" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rhs2" localSheetId="2" hidden="1">'Задача 3 (в4)'!$L$23:$L$24</definedName>
     <definedName name="solver_rhs2" localSheetId="3" hidden="1">'Задача 4 (в4)'!$H$31:$H$33</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="3" hidden="1">100</definedName>
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="3" hidden="1">0.01</definedName>
-    <definedName name="solver_typ" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_ver" localSheetId="3" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_ver" localSheetId="3" hidden="1">2</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -128,7 +161,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="64">
   <si>
     <t>A1</t>
   </si>
@@ -151,12 +184,6 @@
     <t>p</t>
   </si>
   <si>
-    <t>q</t>
-  </si>
-  <si>
-    <t>Ожид. выигр. (игрок А)</t>
-  </si>
-  <si>
     <t>B3</t>
   </si>
   <si>
@@ -182,27 +209,6 @@
   </si>
   <si>
     <t>B5</t>
-  </si>
-  <si>
-    <t>B5 &gt; B4</t>
-  </si>
-  <si>
-    <t>B3 &gt; B2</t>
-  </si>
-  <si>
-    <t>A2 &lt; A3</t>
-  </si>
-  <si>
-    <t>A3 &gt; A1</t>
-  </si>
-  <si>
-    <t>B1 &gt; B3</t>
-  </si>
-  <si>
-    <t>Так как minmax = maxmin, то существует седловая точка (A3, B1)</t>
-  </si>
-  <si>
-    <t>Оптимальные стратегии A3 и B1</t>
   </si>
   <si>
     <t>p1 = x1 * V</t>
@@ -414,12 +420,162 @@
   <si>
     <t>(y1 + y2 + y3) -&gt; max</t>
   </si>
+  <si>
+    <t>Макс</t>
+  </si>
+  <si>
+    <t>Мин</t>
+  </si>
+  <si>
+    <t>(минмакс)</t>
+  </si>
+  <si>
+    <t>максмин -&gt;</t>
+  </si>
+  <si>
+    <t>&lt;- гарант. выигрыш</t>
+  </si>
+  <si>
+    <t>Гарантированный выигрыш А</t>
+  </si>
+  <si>
+    <t>p1 = x1*v</t>
+  </si>
+  <si>
+    <t>p3 = x3*v</t>
+  </si>
+  <si>
+    <t>q2 = y2*v</t>
+  </si>
+  <si>
+    <t>q4 = y4*v</t>
+  </si>
+  <si>
+    <t>v = 1/(x1+x3)</t>
+  </si>
+  <si>
+    <t>v = 1/ (y2+y4)</t>
+  </si>
+  <si>
+    <t>(x1+x3) -&gt; min</t>
+  </si>
+  <si>
+    <t>(y2+y4) -&gt; max</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> *( xi) &gt;= 1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>T</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">x </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  * (x i) &gt;= 1</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">v = </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">y </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>i</t>
+    </r>
+  </si>
+  <si>
+    <t>A * (y i) &lt;= 1</t>
+  </si>
+  <si>
+    <t>(y2+y4)-&gt;max</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -474,8 +630,53 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow (Основной текст)"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow (Основной текст)"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -500,8 +701,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EA72E"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -524,46 +743,97 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -898,27 +1168,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A158CF7-E692-1F45-BD2B-FB54BFD8BF6B}">
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>4</v>
       </c>
       <c r="C1" t="s">
         <v>5</v>
       </c>
+      <c r="D1" t="s">
+        <v>43</v>
+      </c>
       <c r="E1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -928,18 +1198,14 @@
       <c r="C2">
         <v>12</v>
       </c>
+      <c r="D2" s="18">
+        <v>12</v>
+      </c>
       <c r="E2">
-        <v>0.75000000946327894</v>
-      </c>
-      <c r="F2">
-        <v>0.5</v>
-      </c>
-      <c r="H2">
-        <f>B2*$F$2+C2*$F$3</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.7500009533294022</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -949,18 +1215,14 @@
       <c r="C3">
         <v>7</v>
       </c>
+      <c r="D3" s="18">
+        <v>7</v>
+      </c>
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>0.5</v>
-      </c>
-      <c r="H3">
-        <f>B3*$F$2+C3*$F$3</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -970,19 +1232,14 @@
       <c r="C4">
         <v>16</v>
       </c>
+      <c r="D4" s="18">
+        <v>10</v>
+      </c>
       <c r="E4">
-        <v>0.24999999053672095</v>
-      </c>
-      <c r="F4">
-        <f>SUM(F2:F3)</f>
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <f>B4*$F$2+C4*$F$3</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.25000004667059761</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -992,43 +1249,73 @@
       <c r="C5">
         <v>14</v>
       </c>
+      <c r="D5" s="18">
+        <v>11</v>
+      </c>
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="H5">
-        <f>B5*$F$2+C5*$F$3</f>
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="19">
+        <f>MAX(D2:D5)</f>
+        <v>12</v>
+      </c>
       <c r="E6">
         <f>SUM(E2:E5)</f>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="H6" s="1">
-        <f>MAX(H2:H5)</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+        <v>1.0000009999999997</v>
+      </c>
+      <c r="H6" s="20"/>
+    </row>
+    <row r="7" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="B7">
         <f>SUMPRODUCT(E2:E5,B2:B5)</f>
-        <v>13.000000037853114</v>
+        <v>13.000013813317608</v>
       </c>
       <c r="C7">
-        <f>SUMPRODUCT(E2:E5,C2:C5)</f>
-        <v>12.999999962146882</v>
+        <f>SUMPRODUCT(C2:C5,E2:E5)</f>
+        <v>13.000012186682389</v>
       </c>
       <c r="D7" s="1">
         <f>MIN(B7:C7)</f>
-        <v>12.999999962146882</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13.000012186682389</v>
+      </c>
+      <c r="E7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
+      <c r="B8" s="18">
+        <v>10</v>
+      </c>
+      <c r="C8" s="18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="18">
+        <v>14</v>
+      </c>
+      <c r="C9" s="18">
+        <v>16</v>
+      </c>
+      <c r="D9" s="19">
+        <f>MIN(B9:C9)</f>
+        <v>14</v>
+      </c>
+      <c r="E9" t="s">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1038,12 +1325,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F30DACAE-3996-154B-9B89-62D52FA45CAF}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.125" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>4</v>
       </c>
@@ -1051,19 +1338,19 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1088,7 +1375,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1109,7 +1396,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1130,7 +1417,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1151,9 +1438,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <f>MAX(B2:B5)</f>
@@ -1172,23 +1459,23 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1">
         <f>MIN(B6:F6)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1198,10 +1485,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB233ED9-ECB0-A148-880D-C460266E0B9C}">
-  <dimension ref="A1:R15"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:R40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>4</v>
       </c>
@@ -1209,37 +1496,22 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>17</v>
-      </c>
-      <c r="O1" t="s">
-        <v>4</v>
-      </c>
-      <c r="P1" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1255,38 +1527,35 @@
       <c r="E2" s="5">
         <v>4</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="4">
         <v>6</v>
       </c>
-      <c r="H2" t="s">
-        <v>0</v>
+      <c r="H2" s="3">
+        <v>5</v>
       </c>
       <c r="I2" s="3">
+        <v>7</v>
+      </c>
+      <c r="J2" s="6">
+        <v>7</v>
+      </c>
+      <c r="K2" s="7">
+        <v>4</v>
+      </c>
+      <c r="M2" s="6">
         <v>5</v>
       </c>
-      <c r="J2" s="7">
-        <v>7</v>
-      </c>
-      <c r="K2" s="8">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>6</v>
-      </c>
-      <c r="N2" t="s">
-        <v>0</v>
-      </c>
-      <c r="O2" s="3">
-        <v>5</v>
-      </c>
-      <c r="P2" s="9">
-        <v>7</v>
-      </c>
-      <c r="Q2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="N2" s="3">
+        <v>7</v>
+      </c>
+      <c r="O2" s="7">
+        <v>4</v>
+      </c>
+      <c r="P2" s="21"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1302,47 +1571,36 @@
       <c r="E3" s="5">
         <v>3</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="4">
         <v>4</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" t="s">
-        <v>1</v>
+      <c r="G3" s="23"/>
+      <c r="H3" s="3">
+        <v>9</v>
       </c>
       <c r="I3" s="3">
+        <v>3</v>
+      </c>
+      <c r="J3" s="6">
+        <v>8</v>
+      </c>
+      <c r="K3" s="7">
+        <v>3</v>
+      </c>
+      <c r="M3" s="6">
         <v>9</v>
       </c>
-      <c r="J3" s="7">
+      <c r="N3" s="3">
         <v>3</v>
       </c>
-      <c r="K3" s="8">
-        <v>8</v>
-      </c>
-      <c r="L3">
-        <v>4</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N3" t="s">
-        <v>1</v>
-      </c>
       <c r="O3" s="7">
-        <v>9</v>
-      </c>
-      <c r="P3" s="7">
-        <v>8</v>
-      </c>
-      <c r="Q3" s="5">
-        <v>4</v>
-      </c>
-      <c r="R3" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="22"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1358,38 +1616,35 @@
       <c r="E4" s="5">
         <v>7</v>
       </c>
-      <c r="F4" s="6">
-        <v>7</v>
-      </c>
-      <c r="H4" t="s">
-        <v>2</v>
+      <c r="F4" s="4">
+        <v>7</v>
+      </c>
+      <c r="H4" s="3">
+        <v>10</v>
       </c>
       <c r="I4" s="3">
+        <v>1</v>
+      </c>
+      <c r="J4" s="6">
         <v>10</v>
       </c>
-      <c r="J4" s="7">
-        <v>1</v>
-      </c>
-      <c r="K4" s="8">
+      <c r="K4" s="7">
+        <v>7</v>
+      </c>
+      <c r="M4" s="6">
         <v>10</v>
       </c>
-      <c r="L4">
-        <v>7</v>
-      </c>
-      <c r="N4" t="s">
-        <v>2</v>
-      </c>
-      <c r="O4" s="8">
-        <v>10</v>
-      </c>
-      <c r="P4" s="8">
-        <v>10</v>
-      </c>
-      <c r="Q4" s="6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="N4" s="3">
+        <v>1</v>
+      </c>
+      <c r="O4" s="7">
+        <v>7</v>
+      </c>
+      <c r="P4" s="21"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1405,222 +1660,460 @@
       <c r="E5" s="5">
         <v>3</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="4">
         <v>5</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="3">
+        <v>6</v>
+      </c>
+      <c r="I5" s="3">
         <v>3</v>
       </c>
-      <c r="I5" s="3">
+      <c r="J5" s="6">
+        <v>4</v>
+      </c>
+      <c r="K5" s="7">
+        <v>3</v>
+      </c>
+      <c r="M5" s="6">
         <v>6</v>
       </c>
-      <c r="J5" s="7">
+      <c r="N5" s="3">
         <v>3</v>
       </c>
-      <c r="K5" s="8">
+      <c r="O5" s="7">
+        <v>3</v>
+      </c>
+      <c r="P5" s="21"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A7" s="7">
+        <v>7</v>
+      </c>
+      <c r="B7" s="7">
         <v>4</v>
       </c>
-      <c r="L5">
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6">
+        <v>3</v>
+      </c>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="3"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="N5" t="s">
-        <v>3</v>
-      </c>
-      <c r="O5" s="3">
-        <v>6</v>
-      </c>
-      <c r="P5" s="9">
+      <c r="M8" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" t="s">
+        <v>9</v>
+      </c>
+      <c r="O8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
+        <v>1</v>
+      </c>
+      <c r="B9" s="21">
+        <v>7</v>
+      </c>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="L9" s="8">
+        <v>7</v>
+      </c>
+      <c r="M9" s="8">
         <v>4</v>
-      </c>
-      <c r="Q5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K8" s="11"/>
-      <c r="L8" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="M8" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="N8" t="s">
-        <v>11</v>
-      </c>
-      <c r="O8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="7">
-        <v>5</v>
-      </c>
-      <c r="C9" s="7">
-        <v>7</v>
-      </c>
-      <c r="D9" s="7">
-        <v>6</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G9" s="8">
-        <v>10</v>
-      </c>
-      <c r="H9" s="7">
-        <v>10</v>
-      </c>
-      <c r="I9" s="9">
-        <v>7</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="L9" s="11">
-        <v>10</v>
-      </c>
-      <c r="M9" s="11">
-        <v>7</v>
       </c>
       <c r="N9">
         <f>MIN(L9:M9)</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O9" s="1">
         <f>MAX(N9:N10)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A10" s="6">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6">
+        <v>3</v>
+      </c>
+      <c r="C10" s="21"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="3"/>
+      <c r="K10" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="8">
-        <v>10</v>
-      </c>
-      <c r="C10" s="8">
-        <v>10</v>
-      </c>
-      <c r="D10" s="6">
-        <v>7</v>
-      </c>
-      <c r="E10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="8">
-        <v>6</v>
-      </c>
-      <c r="H10" s="7">
-        <v>4</v>
-      </c>
-      <c r="I10" s="3">
-        <v>5</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="11">
-        <v>6</v>
-      </c>
-      <c r="M10" s="11">
-        <v>5</v>
+      <c r="L10" s="8">
+        <v>1</v>
+      </c>
+      <c r="M10" s="8">
+        <v>7</v>
       </c>
       <c r="N10">
-        <f t="shared" ref="N10" si="0">MIN(L10:M10)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="3">
-        <v>6</v>
-      </c>
-      <c r="C11" s="9">
-        <v>4</v>
-      </c>
-      <c r="D11">
-        <v>5</v>
-      </c>
+        <f>MIN(L10:M10)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
       <c r="K11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L11">
         <f>MAX(L9:L10)</f>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M11">
         <f>MAX(M9:M10)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K12" s="13" t="s">
-        <v>14</v>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="K12" t="s">
+        <v>12</v>
       </c>
       <c r="L12" s="1">
         <f>MIN(L11:M11)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K14" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="K15" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="H14" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="K14" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="H15" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="L15" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="H16" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" s="17"/>
+      <c r="K16" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="L16" s="17"/>
+    </row>
+    <row r="17" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="H17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" s="24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="H18" t="s">
+        <v>54</v>
+      </c>
+      <c r="K18" s="24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="5:12" ht="19" x14ac:dyDescent="0.2">
+      <c r="H19" t="s">
+        <v>56</v>
+      </c>
+      <c r="K19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="5:12" ht="20" x14ac:dyDescent="0.25">
+      <c r="E22" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="I22" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="K22" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="5:12" ht="19" x14ac:dyDescent="0.2">
+      <c r="E23" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="I23" s="3">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="K23" cm="1">
+        <f t="array" ref="K23:K24">MMULT(E24:F25,I23:I24)</f>
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E24" s="8">
+        <v>7</v>
+      </c>
+      <c r="F24" s="8">
+        <v>1</v>
+      </c>
+      <c r="G24" s="3"/>
+      <c r="I24" s="3">
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E25" s="8">
+        <v>4</v>
+      </c>
+      <c r="F25" s="8">
+        <v>7</v>
+      </c>
+      <c r="G25" s="3"/>
+      <c r="I25" s="3"/>
+    </row>
+    <row r="26" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+    </row>
+    <row r="27" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="H27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I27" s="1">
+        <f>SUM(I23:I25)</f>
+        <v>0.2</v>
+      </c>
+      <c r="J27" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="H28" t="s">
+        <v>60</v>
+      </c>
+      <c r="I28">
+        <f>1/I27</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="H29" t="s">
+        <v>0</v>
+      </c>
+      <c r="I29" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="H30">
+        <f>I23*I28</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I30">
+        <f>I24*I28</f>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="31" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="H31" s="15">
+        <f>SUM(H30:I30)</f>
+        <v>1</v>
+      </c>
+      <c r="I31" s="15"/>
+    </row>
+    <row r="33" spans="5:12" ht="18" x14ac:dyDescent="0.25">
+      <c r="E33" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="I33" t="s">
+        <v>61</v>
+      </c>
+      <c r="K33" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E34" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E35" s="29">
+        <v>7</v>
+      </c>
+      <c r="F35" s="30">
+        <v>4</v>
+      </c>
+      <c r="G35" s="3"/>
+      <c r="I35">
+        <v>1</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E36" s="31">
+        <v>1</v>
+      </c>
+      <c r="F36" s="32">
+        <v>7</v>
+      </c>
+      <c r="G36" s="3"/>
+    </row>
+    <row r="37" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+    </row>
+    <row r="38" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="I38" t="s">
+        <v>34</v>
+      </c>
+      <c r="J38">
+        <f>I34+I35</f>
+        <v>2</v>
+      </c>
+      <c r="K38" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="I39" t="s">
+        <v>36</v>
+      </c>
+      <c r="J39">
+        <f>1/J38</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="40" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="I40" t="s">
+        <v>5</v>
+      </c>
+      <c r="J40" t="s">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="E34:G34"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00A87396-8CB1-1D49-9001-7761717ACC11}">
-  <dimension ref="A1:U46"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:U40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>4</v>
       </c>
@@ -1628,16 +2121,16 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" t="s">
-        <v>11</v>
-      </c>
       <c r="F1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1659,7 +2152,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1677,7 +2170,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1695,9 +2188,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <f>MAX(B2:B4)</f>
@@ -1712,108 +2205,108 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1">
         <f>MIN(B5:E5)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="17" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B10" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="17" t="s">
+      <c r="C10" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="G10" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H10" s="17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="17" t="s">
+      <c r="H10" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B11" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B12" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="F12" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="17" t="s">
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="19" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="20" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="19" x14ac:dyDescent="0.2">
+      <c r="A19" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="H11" s="17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="F12" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="19.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="G18" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
       <c r="E19">
         <v>3.7890044289698936E-2</v>
       </c>
@@ -1825,7 +2318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>2</v>
       </c>
@@ -1845,7 +2338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>10</v>
       </c>
@@ -1865,7 +2358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>8</v>
       </c>
@@ -1876,77 +2369,77 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="D24" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E24">
         <f>SUM(E19:E21)</f>
         <v>0.11069836548036886</v>
       </c>
       <c r="F24" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="D25" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E25">
         <f>1/E24</f>
         <v>9.0335570508251006</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D26" s="17" t="s">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D26" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="E26" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="17" t="s">
+      <c r="E26" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D27" s="21">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D27" s="13">
         <f>E19*E25</f>
         <v>0.34228187674928517</v>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="13">
         <f>E20*E25</f>
         <v>0.24161073915368764</v>
       </c>
-      <c r="F27" s="21">
+      <c r="F27" s="13">
         <f>E21*E25</f>
         <v>0.41610738409702736</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D28" s="17"/>
-      <c r="E28" s="22">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D28" s="11"/>
+      <c r="E28" s="14">
         <f>SUM(D27:F27)</f>
         <v>1.0000000000000002</v>
       </c>
-      <c r="F28" s="17"/>
-    </row>
-    <row r="30" spans="1:8" ht="18.75" x14ac:dyDescent="0.35">
-      <c r="A30" s="20" t="s">
-        <v>46</v>
+      <c r="F28" s="11"/>
+    </row>
+    <row r="30" spans="1:8" ht="18" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="E30" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="G30" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
       <c r="E31">
         <v>2.9717681691123158E-3</v>
       </c>
@@ -1958,7 +2451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>2</v>
       </c>
@@ -1978,7 +2471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>7</v>
       </c>
@@ -1997,11 +2490,10 @@
       <c r="H33">
         <v>1</v>
       </c>
-      <c r="R33" s="15"/>
-      <c r="T33" s="14"/>
-      <c r="U33" s="14"/>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T33" s="10"/>
+      <c r="U33" s="10"/>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>16</v>
       </c>
@@ -2011,96 +2503,62 @@
       <c r="C34">
         <v>7</v>
       </c>
-      <c r="R34" s="15"/>
-      <c r="T34" s="14"/>
-      <c r="U34" s="14"/>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T34" s="10"/>
+      <c r="U34" s="10"/>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D36" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E36">
         <f>SUM(E31:E33)</f>
         <v>0.1106983654088044</v>
       </c>
       <c r="F36" t="s">
-        <v>50</v>
-      </c>
-      <c r="M36" s="15"/>
-      <c r="N36" s="15"/>
-      <c r="U36" s="15"/>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D37" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E37">
         <f>1/E36</f>
         <v>9.0335570566651295</v>
       </c>
-      <c r="M37" s="15"/>
-      <c r="N37" s="15"/>
-      <c r="U37" s="15"/>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="D38" s="17" t="s">
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="D38" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E38" s="17" t="s">
+      <c r="E38" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="F38" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="M38" s="15"/>
-      <c r="N38" s="15"/>
-      <c r="U38" s="15"/>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="D39" s="21">
+      <c r="F38" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="D39" s="13">
         <f>E31*E37</f>
         <v>2.6845637314857371E-2</v>
       </c>
-      <c r="E39" s="21">
+      <c r="E39" s="13">
         <f>E32*E37</f>
         <v>0.59731544027713801</v>
       </c>
-      <c r="F39" s="21">
+      <c r="F39" s="13">
         <f>E33*E37</f>
         <v>0.37583892240800465</v>
       </c>
-      <c r="M39" s="15"/>
-      <c r="N39" s="15"/>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="D40" s="17"/>
-      <c r="E40" s="21">
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="D40" s="11"/>
+      <c r="E40" s="13">
         <f>SUM(D39:F39)</f>
         <v>1</v>
       </c>
-      <c r="F40" s="17"/>
-      <c r="M40" s="15"/>
-      <c r="N40" s="15"/>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="I42" s="15"/>
-      <c r="K42" s="15"/>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="I43" s="15"/>
-      <c r="K43" s="15"/>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="I44" s="15"/>
-      <c r="K44" s="15"/>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="I45" s="15"/>
-      <c r="K45" s="15"/>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="I46" s="15"/>
-      <c r="K46" s="15"/>
+      <c r="F40" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="4">
